--- a/storage/templates/Comedor.xlsx
+++ b/storage/templates/Comedor.xlsx
@@ -371,7 +371,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -475,6 +475,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6107,12 +6110,14 @@
       </c>
     </row>
     <row r="80" ht="25.05" customHeight="1">
-      <c r="A80" s="12" t="n">
-        <v>581</v>
+      <c r="A80" s="37" t="inlineStr">
+        <is>
+          <t>28370</t>
+        </is>
       </c>
       <c r="B80" s="12" t="inlineStr">
         <is>
-          <t>SIROPE CARAMELO 1000-1200 GR</t>
+          <t>JARABE TE CHAI S/ALCOHOL 70 CL</t>
         </is>
       </c>
       <c r="C80" s="3" t="n">
@@ -6120,11 +6125,11 @@
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>BOTE</t>
+          <t>BOTELLA</t>
         </is>
       </c>
       <c r="E80" s="8" t="n">
-        <v>3.252</v>
+        <v>10.49</v>
       </c>
       <c r="F80" s="20">
         <f>C80*E80</f>
@@ -6175,12 +6180,14 @@
       </c>
     </row>
     <row r="81" ht="25.05" customHeight="1">
-      <c r="A81" s="12" t="n">
-        <v>28370</v>
+      <c r="A81" s="37" t="inlineStr">
+        <is>
+          <t>581</t>
+        </is>
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>JARABE TE CHAI S/ALCOHOL 70 CL</t>
+          <t>SIROPE CARAMELO 1000-1200 GR</t>
         </is>
       </c>
       <c r="C81" s="3" t="n">
@@ -6188,11 +6195,11 @@
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>BOTELLA</t>
+          <t>BOTE</t>
         </is>
       </c>
       <c r="E81" s="8" t="n">
-        <v>10.49</v>
+        <v>3.25241</v>
       </c>
       <c r="F81" s="20">
         <f>C81*E81</f>

--- a/storage/templates/Comedor.xlsx
+++ b/storage/templates/Comedor.xlsx
@@ -806,7 +806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN1002"/>
+  <dimension ref="A1:AN1003"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="25.05" customHeight="1"/>
   <cols>
     <col width="10.77734375" customWidth="1" style="1" min="1" max="1"/>
@@ -6250,68 +6250,90 @@
       </c>
     </row>
     <row r="82" ht="25.05" customHeight="1">
-      <c r="C82" s="3">
-        <f>SUM(C7:C81)</f>
-        <v/>
-      </c>
-      <c r="D82" s="9" t="n"/>
-      <c r="E82" s="10" t="inlineStr">
+      <c r="A82" s="37" t="inlineStr">
+        <is>
+          <t>14573</t>
+        </is>
+      </c>
+      <c r="B82" s="12" t="inlineStr">
+        <is>
+          <t>AGUA SIN GAS CRISTAL AQUABONA C/R 50 CL</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>BOTELLA</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="n">
+        <v>0.1895</v>
+      </c>
+      <c r="F82" s="20">
+        <f>C82*E82</f>
+        <v/>
+      </c>
+      <c r="G82" s="19" t="n"/>
+      <c r="H82" s="19" t="n"/>
+      <c r="I82" s="19" t="n"/>
+      <c r="J82" s="19" t="n"/>
+      <c r="K82" s="19" t="n"/>
+      <c r="L82" s="19" t="n"/>
+      <c r="M82" s="19" t="n"/>
+      <c r="N82" s="19" t="n"/>
+      <c r="O82" s="19" t="n"/>
+      <c r="P82" s="19" t="n"/>
+      <c r="Q82" s="19" t="n"/>
+      <c r="R82" s="19" t="n"/>
+      <c r="S82" s="19" t="n"/>
+      <c r="T82" s="19" t="n"/>
+      <c r="U82" s="19" t="n"/>
+      <c r="V82" s="19" t="n"/>
+      <c r="W82" s="19" t="n"/>
+      <c r="X82" s="19" t="n"/>
+      <c r="Y82" s="19" t="n"/>
+      <c r="Z82" s="19" t="n"/>
+      <c r="AA82" s="19" t="n"/>
+      <c r="AB82" s="19" t="n"/>
+      <c r="AC82" s="19" t="n"/>
+      <c r="AD82" s="19" t="n"/>
+      <c r="AE82" s="19" t="n"/>
+      <c r="AF82" s="19" t="n"/>
+      <c r="AG82" s="19" t="n"/>
+      <c r="AH82" s="19" t="n"/>
+      <c r="AI82" s="19" t="n"/>
+      <c r="AJ82" s="19" t="n"/>
+      <c r="AK82" s="19" t="n"/>
+      <c r="AL82" s="22">
+        <f>SUM(G82:AK82)</f>
+        <v/>
+      </c>
+      <c r="AM82" s="23">
+        <f>SUM(C82,AL82)</f>
+        <v/>
+      </c>
+      <c r="AN82" s="24">
+        <f>E82*AM82</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" ht="25.05" customHeight="1">
+      <c r="C83" s="3">
+        <f>SUM(C7:C82)</f>
+        <v/>
+      </c>
+      <c r="D83" s="9" t="n"/>
+      <c r="E83" s="10" t="inlineStr">
         <is>
           <t>ESTOCAJE  INICIAL</t>
         </is>
       </c>
-      <c r="F82" s="11">
-        <f>SUM(F7:F81)</f>
-        <v/>
-      </c>
-      <c r="G82" s="12" t="n"/>
-      <c r="H82" s="12" t="n"/>
-      <c r="I82" s="12" t="n"/>
-      <c r="J82" s="12" t="n"/>
-      <c r="K82" s="12" t="n"/>
-      <c r="L82" s="12" t="n"/>
-      <c r="M82" s="12" t="n"/>
-      <c r="N82" s="12" t="n"/>
-      <c r="O82" s="12" t="n"/>
-      <c r="P82" s="12" t="n"/>
-      <c r="Q82" s="12" t="n"/>
-      <c r="R82" s="12" t="n"/>
-      <c r="S82" s="12" t="n"/>
-      <c r="T82" s="12" t="n"/>
-      <c r="U82" s="12" t="n"/>
-      <c r="V82" s="12" t="n"/>
-      <c r="W82" s="12" t="n"/>
-      <c r="X82" s="12" t="n"/>
-      <c r="Y82" s="12" t="n"/>
-      <c r="Z82" s="12" t="n"/>
-      <c r="AA82" s="12" t="n"/>
-      <c r="AB82" s="12" t="n"/>
-      <c r="AC82" s="12" t="n"/>
-      <c r="AD82" s="12" t="n"/>
-      <c r="AE82" s="12" t="n"/>
-      <c r="AF82" s="12" t="n"/>
-      <c r="AG82" s="12" t="n"/>
-      <c r="AH82" s="12" t="n"/>
-      <c r="AI82" s="12" t="n"/>
-      <c r="AJ82" s="12" t="n"/>
-      <c r="AK82" s="12" t="n"/>
-      <c r="AL82" s="12">
-        <f>SUM(AL7:AL81)</f>
-        <v/>
-      </c>
-      <c r="AM82" s="12">
-        <f>SUM(AM7:AM81)</f>
-        <v/>
-      </c>
-      <c r="AN82" s="25">
-        <f>SUM(AN7:AN81)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83" ht="25.05" customHeight="1">
-      <c r="D83" s="9" t="n"/>
-      <c r="E83" s="12" t="n"/>
-      <c r="F83" s="12" t="n"/>
+      <c r="F83" s="11">
+        <f>SUM(F7:F82)</f>
+        <v/>
+      </c>
       <c r="G83" s="12" t="n"/>
       <c r="H83" s="12" t="n"/>
       <c r="I83" s="12" t="n"/>
@@ -6343,9 +6365,18 @@
       <c r="AI83" s="12" t="n"/>
       <c r="AJ83" s="12" t="n"/>
       <c r="AK83" s="12" t="n"/>
-      <c r="AL83" s="12" t="n"/>
-      <c r="AM83" s="12" t="n"/>
-      <c r="AN83" s="12" t="n"/>
+      <c r="AL83" s="12">
+        <f>SUM(AL7:AL82)</f>
+        <v/>
+      </c>
+      <c r="AM83" s="12">
+        <f>SUM(AM7:AM82)</f>
+        <v/>
+      </c>
+      <c r="AN83" s="25">
+        <f>SUM(AN7:AN82)</f>
+        <v/>
+      </c>
     </row>
     <row r="84" ht="25.05" customHeight="1">
       <c r="D84" s="9" t="n"/>
@@ -6423,9 +6454,11 @@
       <c r="AK85" s="12" t="n"/>
       <c r="AL85" s="12" t="n"/>
       <c r="AM85" s="12" t="n"/>
+      <c r="AN85" s="12" t="n"/>
     </row>
     <row r="86" ht="25.05" customHeight="1">
       <c r="D86" s="9" t="n"/>
+      <c r="E86" s="12" t="n"/>
       <c r="F86" s="12" t="n"/>
       <c r="G86" s="12" t="n"/>
       <c r="H86" s="12" t="n"/>
@@ -6460,7 +6493,6 @@
       <c r="AK86" s="12" t="n"/>
       <c r="AL86" s="12" t="n"/>
       <c r="AM86" s="12" t="n"/>
-      <c r="AN86" s="12" t="n"/>
     </row>
     <row r="87" ht="25.05" customHeight="1">
       <c r="D87" s="9" t="n"/>
@@ -7148,6 +7180,41 @@
     </row>
     <row r="105" ht="25.05" customHeight="1">
       <c r="D105" s="9" t="n"/>
+      <c r="F105" s="12" t="n"/>
+      <c r="G105" s="12" t="n"/>
+      <c r="H105" s="12" t="n"/>
+      <c r="I105" s="12" t="n"/>
+      <c r="J105" s="12" t="n"/>
+      <c r="K105" s="12" t="n"/>
+      <c r="L105" s="12" t="n"/>
+      <c r="M105" s="12" t="n"/>
+      <c r="N105" s="12" t="n"/>
+      <c r="O105" s="12" t="n"/>
+      <c r="P105" s="12" t="n"/>
+      <c r="Q105" s="12" t="n"/>
+      <c r="R105" s="12" t="n"/>
+      <c r="S105" s="12" t="n"/>
+      <c r="T105" s="12" t="n"/>
+      <c r="U105" s="12" t="n"/>
+      <c r="V105" s="12" t="n"/>
+      <c r="W105" s="12" t="n"/>
+      <c r="X105" s="12" t="n"/>
+      <c r="Y105" s="12" t="n"/>
+      <c r="Z105" s="12" t="n"/>
+      <c r="AA105" s="12" t="n"/>
+      <c r="AB105" s="12" t="n"/>
+      <c r="AC105" s="12" t="n"/>
+      <c r="AD105" s="12" t="n"/>
+      <c r="AE105" s="12" t="n"/>
+      <c r="AF105" s="12" t="n"/>
+      <c r="AG105" s="12" t="n"/>
+      <c r="AH105" s="12" t="n"/>
+      <c r="AI105" s="12" t="n"/>
+      <c r="AJ105" s="12" t="n"/>
+      <c r="AK105" s="12" t="n"/>
+      <c r="AL105" s="12" t="n"/>
+      <c r="AM105" s="12" t="n"/>
+      <c r="AN105" s="12" t="n"/>
     </row>
     <row r="106" ht="25.05" customHeight="1">
       <c r="D106" s="9" t="n"/>
@@ -9839,6 +9906,9 @@
     </row>
     <row r="1002">
       <c r="D1002" s="9" t="n"/>
+    </row>
+    <row r="1003">
+      <c r="D1003" s="9" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A6:F6"/>
